--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="134">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -114,10 +114,6 @@
   </si>
   <si>
     <t>macron</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"job":"trader","gold":200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -602,6 +598,14 @@
 "b":{"l":16,"r":16,"t":32,"b":0},                    
 "g":{"l":16,"r":16,"t":32,"b":0},
 "z":{"l":16,"r":16,"t":32,"b":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"innkeeper","gold":200,"style":"weak"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"trader","gold":200,"style":"weak"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -978,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -986,7 +990,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -994,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1010,7 +1014,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1023,10 +1027,10 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1065,13 +1069,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>22</v>
@@ -1085,22 +1089,22 @@
         <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1108,22 +1112,22 @@
         <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1134,19 +1138,19 @@
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="124.8">
@@ -1154,22 +1158,22 @@
         <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="46.8">
@@ -1180,10 +1184,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>17</v>
@@ -1194,25 +1198,25 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1220,194 +1224,194 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1415,16 +1419,16 @@
         <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1432,16 +1436,16 @@
         <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1449,16 +1453,16 @@
         <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1466,16 +1470,16 @@
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1483,16 +1487,16 @@
         <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1500,16 +1504,16 @@
         <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1517,16 +1521,16 @@
         <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1550,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1558,7 +1562,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1566,7 +1570,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1574,7 +1578,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="124.8">
@@ -1582,7 +1586,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1592,10 +1596,10 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="31.2">
@@ -1611,7 +1615,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
@@ -97,10 +97,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"job":"ranger","gold":100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>musk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -606,6 +602,10 @@
   </si>
   <si>
     <t>"job":"trader","gold":200,"style":"weak"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"ranger","gold":100,"survival":true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -982,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -990,7 +990,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -998,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1006,7 +1006,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="140.4">
@@ -1014,7 +1014,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1027,10 +1027,10 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1066,22 +1066,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1089,22 +1089,22 @@
         <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1112,22 +1112,22 @@
         <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1138,19 +1138,19 @@
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="124.8">
@@ -1158,22 +1158,22 @@
         <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="46.8">
@@ -1184,10 +1184,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>17</v>
@@ -1198,25 +1198,25 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1224,194 +1224,194 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1419,16 +1419,16 @@
         <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1436,16 +1436,16 @@
         <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1453,16 +1453,16 @@
         <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1470,16 +1470,16 @@
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1487,16 +1487,16 @@
         <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1504,16 +1504,16 @@
         <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1521,16 +1521,16 @@
         <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1554,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1562,7 +1562,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1570,7 +1570,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1578,7 +1578,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="124.8">
@@ -1586,7 +1586,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="31.2">
@@ -1615,7 +1615,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
@@ -113,10 +113,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"job":"butcher","gold":200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"job":"merchant","gold":200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -542,18 +538,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"body":{"sprite":"musk","scale":0.25,"y":32},
-"hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16}, 
-"w":64, "h":64,
-"b":{"l":16,"r":16,"t":32,"b":0},                    
-"g":{"l":16,"r":16,"t":32,"b":0},
-"z":{"l":16,"r":16,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"sprite":"rip","scale":0.5,"y":32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"innkeeper","gold":200,"style":"weak"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"trader","gold":200,"style":"weak"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"ranger","gold":100,"survival":true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -561,17 +558,28 @@
 "faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":64, "h":64,
-"b":{"l":16,"r":16,"t":32,"b":0},                    
+"b":{"l":16,"r":16,"t":32,"b":0},
 "g":{"l":16,"r":16,"t":32,"b":0},
 "z":{"l":16,"r":16,"t":32,"b":0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>"body":{"sprite":"musk","scale":0.25,"y":32},
+"hand":{"sprite":"hand-man","scale":0.25,"y":32},
+"faceR":true,
+"anchor":{"x":0,"y":16},
+"w":64, "h":64,
+"b":{"l":16,"r":16,"t":32,"b":0},
+"g":{"l":16,"r":16,"t":32,"b":0},
+"z":{"l":16,"r":16,"t":32,"b":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>"body":{"sprite":"xi","scale":0.25,"y":32},
 "faceR":true,
-"anchor":{"x":0,"y":16}, 
+"anchor":{"x":0,"y":16},
 "w":64, "h":64,
-"b":{"l":16,"r":16,"t":32,"b":0},                    
+"b":{"l":16,"r":16,"t":32,"b":0},
 "g":{"l":16,"r":16,"t":32,"b":0},
 "z":{"l":16,"r":16,"t":32,"b":0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -581,7 +589,7 @@
 "faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":64, "h":64,
-"b":{"l":16,"r":16,"t":32,"b":0},                    
+"b":{"l":16,"r":16,"t":32,"b":0},
 "g":{"l":16,"r":16,"t":32,"b":0},
 "z":{"l":16,"r":16,"t":32,"b":0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -591,21 +599,14 @@
 "faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":64, "h":64,
-"b":{"l":16,"r":16,"t":32,"b":0},                    
+"b":{"l":16,"r":16,"t":32,"b":0},
 "g":{"l":16,"r":16,"t":32,"b":0},
 "z":{"l":16,"r":16,"t":32,"b":0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"job":"innkeeper","gold":200,"style":"weak"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"job":"trader","gold":200,"style":"weak"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"job":"ranger","gold":100,"survival":true</t>
+    <t>"job":"butcher","gold":200,
+"abilities":["fireball","heal"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -982,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -990,7 +991,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -998,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1006,7 +1007,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="140.4">
@@ -1014,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1027,10 +1028,10 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1069,13 +1070,13 @@
         <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>21</v>
@@ -1089,22 +1090,22 @@
         <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1112,25 +1113,25 @@
         <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="31.2">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1138,19 +1139,19 @@
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="124.8">
@@ -1158,22 +1159,22 @@
         <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="46.8">
@@ -1184,10 +1185,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>17</v>
@@ -1198,25 +1199,25 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1224,194 +1225,194 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1419,16 +1420,16 @@
         <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1436,16 +1437,16 @@
         <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1453,16 +1454,16 @@
         <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1470,16 +1471,16 @@
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1487,16 +1488,16 @@
         <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1504,16 +1505,16 @@
         <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1521,16 +1522,16 @@
         <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1554,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1562,7 +1563,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1570,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1578,7 +1579,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="124.8">
@@ -1586,7 +1587,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1596,10 +1597,10 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="31.2">
@@ -1615,7 +1616,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
@@ -515,29 +515,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"body":{"sprite":"body-man","scale":0.25,"y":32},
-"hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"head":{"sprite":"head-wick","scale":0.25,"y":3.5},
-"faceR":true,
-"anchor":{"x":0,"y":16}, 
-"w":32, "h":64,
-"b":{"l":0,"r":0,"t":32,"b":0},                    
-"g":{"l":0,"r":0,"t":32,"b":0},
-"z":{"l":0,"r":0,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"body":{"sprite":"rogue","scale":0.25,"y":32},
-"hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16}, 
-"w":32, "h":64,
-"b":{"l":0,"r":0,"t":32,"b":0},                    
-"g":{"l":0,"r":0,"t":32,"b":0},
-"z":{"l":0,"r":0,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"sprite":"rip","scale":0.5,"y":32</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -607,6 +584,29 @@
   <si>
     <t>"job":"butcher","gold":200,
 "abilities":["fireball","heal"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"body-man","scale":0.25,"y":32},
+"hand":{"sprite":"hand-man","scale":0.25,"y":32},
+"head":{"sprite":"head-wick","scale":0.25,"y":3.5},
+"faceR":true,
+"anchor":{"x":0,"y":16}, 
+"w":32, "h":64,
+"b":{"l":0,"r":0,"t":32,"b":0},
+"g":{"l":0,"r":0,"t":32,"b":0},
+"z":{"l":0,"r":0,"t":32,"b":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"rogue","scale":0.25,"y":32},
+"hand":{"sprite":"hand-man","scale":0.25,"y":32},
+"faceR":true,
+"anchor":{"x":0,"y":16}, 
+"w":32, "h":64,
+"b":{"l":0,"r":0,"t":32,"b":0},
+"g":{"l":0,"r":0,"t":32,"b":0},
+"z":{"l":0,"r":0,"t":32,"b":0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -999,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1007,7 +1007,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="140.4">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1113,22 +1113,22 @@
         <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="31.2">
@@ -1139,16 +1139,16 @@
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>23</v>
@@ -1159,22 +1159,22 @@
         <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="46.8">
@@ -1571,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1587,7 +1587,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
@@ -531,57 +531,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"body":{"sprite":"melanie","scale":0.25,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16}, 
-"w":64, "h":64,
-"b":{"l":16,"r":16,"t":32,"b":0},
-"g":{"l":16,"r":16,"t":32,"b":0},
-"z":{"l":16,"r":16,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"body":{"sprite":"musk","scale":0.25,"y":32},
-"hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16},
-"w":64, "h":64,
-"b":{"l":16,"r":16,"t":32,"b":0},
-"g":{"l":16,"r":16,"t":32,"b":0},
-"z":{"l":16,"r":16,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"body":{"sprite":"xi","scale":0.25,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16},
-"w":64, "h":64,
-"b":{"l":16,"r":16,"t":32,"b":0},
-"g":{"l":16,"r":16,"t":32,"b":0},
-"z":{"l":16,"r":16,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"body":{"sprite":"macron","scale":0.25,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16}, 
-"w":64, "h":64,
-"b":{"l":16,"r":16,"t":32,"b":0},
-"g":{"l":16,"r":16,"t":32,"b":0},
-"z":{"l":16,"r":16,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"body":{"sprite":"trump","scale":0.25,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16}, 
-"w":64, "h":64,
-"b":{"l":16,"r":16,"t":32,"b":0},
-"g":{"l":16,"r":16,"t":32,"b":0},
-"z":{"l":16,"r":16,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"job":"butcher","gold":200,
 "abilities":["fireball","heal"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -603,6 +552,57 @@
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "faceR":true,
 "anchor":{"x":0,"y":16}, 
+"w":32, "h":64,
+"b":{"l":0,"r":0,"t":32,"b":0},
+"g":{"l":0,"r":0,"t":32,"b":0},
+"z":{"l":0,"r":0,"t":32,"b":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"macron","scale":0.25,"y":32},
+"faceR":true,
+"anchor":{"x":0,"y":16}, 
+"w":32, "h":64,
+"b":{"l":0,"r":0,"t":32,"b":0},
+"g":{"l":0,"r":0,"t":32,"b":0},
+"z":{"l":0,"r":0,"t":32,"b":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"trump","scale":0.25,"y":32},
+"faceR":true,
+"anchor":{"x":0,"y":16}, 
+"w":32, "h":64,
+"b":{"l":0,"r":0,"t":32,"b":0},
+"g":{"l":0,"r":0,"t":32,"b":0},
+"z":{"l":0,"r":0,"t":32,"b":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"melanie","scale":0.25,"y":32},
+"faceR":true,
+"anchor":{"x":0,"y":16}, 
+"w":32, "h":64,
+"b":{"l":0,"r":0,"t":32,"b":0},
+"g":{"l":0,"r":0,"t":32,"b":0},
+"z":{"l":0,"r":0,"t":32,"b":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"musk","scale":0.25,"y":32},
+"hand":{"sprite":"hand-man","scale":0.25,"y":32},
+"faceR":true,
+"anchor":{"x":0,"y":16},
+"w":32, "h":64,
+"b":{"l":0,"r":0,"t":32,"b":0},
+"g":{"l":0,"r":0,"t":32,"b":0},
+"z":{"l":0,"r":0,"t":32,"b":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"xi","scale":0.25,"y":32},
+"faceR":true,
+"anchor":{"x":0,"y":16},
 "w":32, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
 "g":{"l":0,"r":0,"t":32,"b":0},
@@ -971,11 +971,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="52.88671875" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="52.875" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1010,12 +1010,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="140.4">
+    <row r="5" spans="1:2" ht="141.75">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1050,16 +1050,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="66" style="1" customWidth="1"/>
     <col min="3" max="3" width="69" style="1" customWidth="1"/>
-    <col min="4" max="4" width="67.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="67.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="69" style="1" customWidth="1"/>
-    <col min="6" max="6" width="67.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="70.6640625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="67.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="70.625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1131,7 +1131,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.2">
+    <row r="4" spans="1:7" ht="31.5">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,13 +1148,13 @@
         <v>124</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="124.8">
+    <row r="5" spans="1:7" ht="126">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1162,22 +1162,22 @@
         <v>130</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="46.8">
+    <row r="6" spans="1:7" ht="47.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -1544,10 +1544,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="52.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="52.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1582,12 +1582,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="124.8">
+    <row r="5" spans="1:2" ht="126">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1603,7 +1603,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="31.2">
+    <row r="8" spans="1:2" ht="31.5">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="46.8">
+    <row r="9" spans="1:2" ht="47.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -16,13 +16,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="131">
   <si>
     <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>corpse</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -68,10 +64,6 @@
   </si>
   <si>
     <t>icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>corpse</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -515,10 +507,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"sprite":"rip","scale":0.5,"y":32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"job":"innkeeper","gold":200,"style":"weak"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -536,9 +524,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"body":{"sprite":"body-man","scale":0.25,"y":32},
-"hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"head":{"sprite":"head-wick","scale":0.25,"y":3.5},
+    <t>"body":{"sprite":"macron","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32},
 "faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":32, "h":64,
@@ -548,8 +535,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"body":{"sprite":"rogue","scale":0.25,"y":32},
+    <t>"body":{"sprite":"body-man","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
+"head":{"sprite":"head-wick","scale":0.25,"y":3.5},
+"corpse":{"sprite":"rip","scale":0.5,"y":32},
 "faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":32, "h":64,
@@ -559,7 +548,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"body":{"sprite":"macron","scale":0.25,"y":32},
+    <t>"body":{"sprite":"rogue","scale":0.25,"y":32},
+"hand":{"sprite":"hand-man","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32},
 "faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":32, "h":64,
@@ -570,6 +561,7 @@
   </si>
   <si>
     <t>"body":{"sprite":"trump","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32},
 "faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":32, "h":64,
@@ -580,6 +572,7 @@
   </si>
   <si>
     <t>"body":{"sprite":"melanie","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32},
 "faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":32, "h":64,
@@ -591,6 +584,7 @@
   <si>
     <t>"body":{"sprite":"musk","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32},
 "faceR":true,
 "anchor":{"x":0,"y":16},
 "w":32, "h":64,
@@ -601,6 +595,7 @@
   </si>
   <si>
     <t>"body":{"sprite":"xi","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32},
 "faceR":true,
 "anchor":{"x":0,"y":16},
 "w":32, "h":64,
@@ -970,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
@@ -983,62 +978,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="157.5">
       <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="141.75">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>127</v>
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>118</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="B7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1049,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="12.375" style="1" customWidth="1"/>
@@ -1067,471 +1054,448 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="31.5">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="141.75">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="31.5">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="47.25">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="126">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="47.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>119</v>
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>119</v>
+        <v>55</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1543,7 +1507,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
@@ -1555,75 +1519,67 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="141.75">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="126">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="31.5">
+      <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="31.5">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.25">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="47.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
@@ -16,13 +16,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="132">
   <si>
     <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bag</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -72,10 +68,6 @@
   </si>
   <si>
     <t>shape</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bag</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -524,9 +516,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"body":{"sprite":"macron","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32},
-"faceR":true,
+    <t>view</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":32, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -535,73 +529,46 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>"body":{"sprite":"melanie","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"xi","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"macron","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"trump","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"rogue","scale":0.25,"y":32},
+"hand":{"sprite":"hand-man","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>"body":{"sprite":"body-man","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "head":{"sprite":"head-wick","scale":0.25,"y":3.5},
-"corpse":{"sprite":"rip","scale":0.5,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16}, 
-"w":32, "h":64,
-"b":{"l":0,"r":0,"t":32,"b":0},
-"g":{"l":0,"r":0,"t":32,"b":0},
-"z":{"l":0,"r":0,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"body":{"sprite":"rogue","scale":0.25,"y":32},
-"hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16}, 
-"w":32, "h":64,
-"b":{"l":0,"r":0,"t":32,"b":0},
-"g":{"l":0,"r":0,"t":32,"b":0},
-"z":{"l":0,"r":0,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"body":{"sprite":"trump","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16}, 
-"w":32, "h":64,
-"b":{"l":0,"r":0,"t":32,"b":0},
-"g":{"l":0,"r":0,"t":32,"b":0},
-"z":{"l":0,"r":0,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"body":{"sprite":"melanie","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16}, 
-"w":32, "h":64,
-"b":{"l":0,"r":0,"t":32,"b":0},
-"g":{"l":0,"r":0,"t":32,"b":0},
-"z":{"l":0,"r":0,"t":32,"b":0}</t>
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"body":{"sprite":"musk","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16},
-"w":32, "h":64,
-"b":{"l":0,"r":0,"t":32,"b":0},
-"g":{"l":0,"r":0,"t":32,"b":0},
-"z":{"l":0,"r":0,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"body":{"sprite":"xi","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32},
-"faceR":true,
-"anchor":{"x":0,"y":16},
-"w":32, "h":64,
-"b":{"l":0,"r":0,"t":32,"b":0},
-"g":{"l":0,"r":0,"t":32,"b":0},
-"z":{"l":0,"r":0,"t":32,"b":0}</t>
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -965,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
@@ -978,54 +945,62 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="94.5">
+      <c r="A4" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="157.5">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B4" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="63">
       <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1036,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="12.375" style="1" customWidth="1"/>
@@ -1054,448 +1029,471 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="31.5">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="94.5">
+      <c r="A4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="141.75">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="47.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="47.25">
       <c r="A6" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>116</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>72</v>
+        <v>115</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1507,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
@@ -1519,67 +1517,75 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="141.75">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>122</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="47.25">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="31.5">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="31.5">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="47.25">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="47.25">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="131">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,12 +71,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"capacity":-1,
-"items":["sword_01",
-{"id":"helmet_01","count":1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"job":"innkeeper","gold":200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -438,18 +432,6 @@
   </si>
   <si>
     <t>"t":"14:40~14:50", "p":"stair-up~melanie-p1", "map":"trump-inn-f1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"capacity":-1,
-"items":["sword_01",
-{"id":"helmet_01","count":1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"capacity":-1,
-"items":["sword_01","chest_01","gloves_01","chest_02",
-{"id":"helmet_01","count":1}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -569,6 +551,16 @@
   </si>
   <si>
     <t>storage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"capacity":-1,
+"items":["sword_01",{"id":"helmet_01","count":1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"capacity":-1,
+"items":["sword_01","chest_01","gloves_01","chest_02",{"id":"helmet_01","count":1}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -945,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -953,7 +945,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -961,15 +953,15 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="63">
@@ -977,12 +969,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -990,10 +982,10 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1017,7 +1009,7 @@
     <col min="1" max="1" width="12.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="66" style="1" customWidth="1"/>
     <col min="3" max="3" width="69" style="1" customWidth="1"/>
-    <col min="4" max="4" width="67.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="76" style="1" customWidth="1"/>
     <col min="5" max="5" width="69" style="1" customWidth="1"/>
     <col min="6" max="6" width="67.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="70.625" style="1" customWidth="1"/>
@@ -1029,22 +1021,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1052,22 +1044,22 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="31.5">
@@ -1075,45 +1067,45 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="47.25">
@@ -1121,65 +1113,65 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="31.5">
+      <c r="A6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="47.25">
-      <c r="A6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>13</v>
+        <v>129</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>13</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1187,194 +1179,194 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1382,16 +1374,16 @@
         <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1399,16 +1391,16 @@
         <v>6</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1416,16 +1408,16 @@
         <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1433,16 +1425,16 @@
         <v>6</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1450,16 +1442,16 @@
         <v>6</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1467,16 +1459,16 @@
         <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1484,16 +1476,16 @@
         <v>6</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1517,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1525,7 +1517,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1533,15 +1525,15 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="47.25">
@@ -1549,20 +1541,20 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="31.5">
@@ -1578,7 +1570,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -493,11 +493,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"job":"butcher","gold":200,
-"abilities":["fireball","heal"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>view</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -561,6 +556,11 @@
   <si>
     <t>"capacity":-1,
 "items":["sword_01","chest_01","gloves_01","chest_02",{"id":"helmet_01","count":1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"butcher","gold":200,
+"abilities":["fireball","heal"],"meat":"raw_meat"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -958,10 +958,10 @@
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="63">
@@ -969,12 +969,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -1079,7 +1079,7 @@
         <v>116</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>18</v>
@@ -1087,25 +1087,25 @@
     </row>
     <row r="4" spans="1:7" ht="94.5">
       <c r="A4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="47.25">
@@ -1113,42 +1113,42 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="31.5">
       <c r="A6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1530,10 +1530,10 @@
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="47.25">
@@ -1541,12 +1541,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
     <sheet name="brooklyn" sheetId="4" r:id="rId2"/>
-    <sheet name="monster" sheetId="2" r:id="rId3"/>
+    <sheet name="rogues" sheetId="5" r:id="rId3"/>
+    <sheet name="monsters" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="135">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -561,6 +562,28 @@
   <si>
     <t>"job":"butcher","gold":200,
 "abilities":["fireball","heal"],"meat":"raw_meat"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"faceR":false,
+"anchor":{"x":0,"y":16}, 
+"w":64, "h":64,
+"b":{"l":0,"r":0,"t":32,"b":0},
+"g":{"l":0,"r":0,"t":32,"b":0},
+"z":{"l":0,"r":0,"t":32,"b":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monsters:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"monsters:0","scale":2,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1501,7 +1524,7 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="52.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1555,6 +1578,93 @@
       </c>
       <c r="B7" s="1" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="31.5">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="47.25">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="63" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="94.5">
+      <c r="A4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="31.5">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="31.5">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="136">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -584,6 +584,15 @@
   <si>
     <t>"body":{"sprite":"monsters:0","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"faceR":true,
+"anchor":{"x":0,"y":16}, 
+"w":64, "h":64,
+"b":{"l":0,"r":0,"t":32,"b":0},
+"g":{"l":0,"r":0,"t":32,"b":0},
+"z":{"l":0,"r":0,"t":32,"b":0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -984,7 +993,7 @@
         <v>118</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="63">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -588,7 +588,7 @@
   </si>
   <si>
     <t>"faceR":true,
-"anchor":{"x":0,"y":16}, 
+"anchor":{"x":-16,"y":16}, 
 "w":64, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
 "g":{"l":0,"r":0,"t":32,"b":0},

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="135">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -569,15 +569,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"faceR":false,
-"anchor":{"x":0,"y":16}, 
-"w":64, "h":64,
-"b":{"l":0,"r":0,"t":32,"b":0},
-"g":{"l":0,"r":0,"t":32,"b":0},
-"z":{"l":0,"r":0,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>monsters:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -587,7 +578,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"faceR":true,
+    <t>"faceR":false,
 "anchor":{"x":-16,"y":16}, 
 "w":64, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -993,7 +984,7 @@
         <v>118</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="63">
@@ -1639,7 +1630,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1655,7 +1646,7 @@
         <v>118</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5">
@@ -1663,7 +1654,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="136">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -579,6 +579,15 @@
   </si>
   <si>
     <t>"faceR":false,
+"anchor":{"x":-16,"y":16}, 
+"w":64, "h":64,
+"b":{"l":0,"r":0,"t":32,"b":0},
+"g":{"l":0,"r":0,"t":32,"b":0},
+"z":{"l":0,"r":0,"t":32,"b":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"faceR":true,
 "anchor":{"x":-16,"y":16}, 
 "w":64, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -984,7 +993,7 @@
         <v>118</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="63">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="135">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -579,15 +579,6 @@
   </si>
   <si>
     <t>"faceR":false,
-"anchor":{"x":-16,"y":16}, 
-"w":64, "h":64,
-"b":{"l":0,"r":0,"t":32,"b":0},
-"g":{"l":0,"r":0,"t":32,"b":0},
-"z":{"l":0,"r":0,"t":32,"b":0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"faceR":true,
 "anchor":{"x":-16,"y":16}, 
 "w":64, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -993,7 +984,7 @@
         <v>118</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="63">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,20 +4,21 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
     <sheet name="brooklyn" sheetId="4" r:id="rId2"/>
     <sheet name="rogues" sheetId="5" r:id="rId3"/>
     <sheet name="monsters" sheetId="2" r:id="rId4"/>
+    <sheet name="animals" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="142">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -584,6 +585,36 @@
 "b":{"l":0,"r":0,"t":32,"b":0},
 "g":{"l":0,"r":0,"t":32,"b":0},
 "z":{"l":0,"r":0,"t":32,"b":0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wolf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>animals:42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"animals:42","scale":2,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>horse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>animals:82</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"body":{"sprite":"animals:82","scale":2,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"meat":"raw_meat"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1694,4 +1725,113 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
+    <col min="2" max="3" width="63" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="94.5">
+      <c r="A4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="31.5">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="31.5">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="47.25">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="143">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -480,10 +480,6 @@
   </si>
   <si>
     <t>"job":"rogue","gold":200,"type":"enemy"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"job":"innkeeper","gold":200,"style":"weak"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -614,7 +610,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"meat":"raw_meat"</t>
+    <t>"job":"innkeeper","gold":200,"style":"passive_coward"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"meat":"raw_meat","style":"aggressive"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"meat":"raw_meat","style":"skittish"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1007,15 +1011,15 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="63">
@@ -1023,12 +1027,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -1124,16 +1128,16 @@
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>18</v>
@@ -1141,25 +1145,25 @@
     </row>
     <row r="4" spans="1:7" ht="94.5">
       <c r="A4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="47.25">
@@ -1167,42 +1171,42 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="31.5">
       <c r="A6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1584,10 +1588,10 @@
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="47.25">
@@ -1595,12 +1599,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1653,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1661,7 +1665,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1674,10 +1678,10 @@
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5">
@@ -1685,12 +1689,12 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1741,10 +1745,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1752,10 +1756,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1766,18 +1770,18 @@
         <v>141</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="31.5">
@@ -1785,15 +1789,15 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="141">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -29,10 +29,6 @@
   </si>
   <si>
     <t>states</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shape</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -41,10 +37,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>others</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>schedule</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -62,14 +54,6 @@
   </si>
   <si>
     <t>icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>others</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shape</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -488,10 +472,6 @@
   </si>
   <si>
     <t>"job":"ranger","gold":100,"survival":true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>view</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -619,6 +599,18 @@
   </si>
   <si>
     <t>"meat":"raw_meat","style":"skittish"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_view</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_shape</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_others</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -995,60 +987,60 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="63">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" s="3"/>
     </row>
@@ -1079,471 +1071,471 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="31.5">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="47.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="31.5">
       <c r="A6" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1567,52 +1559,52 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="47.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="31.5">
@@ -1620,7 +1612,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="47.25">
@@ -1628,12 +1620,12 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" s="3"/>
     </row>
@@ -1657,49 +1649,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="31.5">
@@ -1707,7 +1699,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="47.25">
@@ -1715,12 +1707,12 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" s="3"/>
     </row>
@@ -1745,64 +1737,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="31.5">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="31.5">
@@ -1810,10 +1802,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="47.25">
@@ -1821,15 +1813,15 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="140">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -41,10 +41,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"capacity":20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>icon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -57,10 +53,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"job":"innkeeper","gold":200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>musk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -74,10 +66,6 @@
   </si>
   <si>
     <t>macron</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"job":"merchant","gold":200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -443,18 +431,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>equips</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>["sword_01"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"job":"smith","gold":200,"weapon":"sword_01"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"str":10, "dex":10, "con":10, "int":10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -464,10 +440,6 @@
   </si>
   <si>
     <t>"job":"rogue","gold":200,"type":"enemy"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"job":"trader","gold":200,"style":"weak"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -523,25 +495,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>storage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"capacity":-1,
-"items":["sword_01",{"id":"helmet_01","count":1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"capacity":-1,
-"items":["sword_01","chest_01","gloves_01","chest_02",{"id":"helmet_01","count":1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"job":"butcher","gold":200,
-"abilities":["fireball","heal"],"meat":"raw_meat"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>orc</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -590,10 +543,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"job":"innkeeper","gold":200,"style":"passive_coward"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"meat":"raw_meat","style":"aggressive"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -611,6 +560,53 @@
   </si>
   <si>
     <t>_others</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"storage":{"capacity":20}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"storage":{"capacity":-1,
+"items":["sword_01",{"id":"helmet_01","count":1}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"storage":{"capacity":-1,
+"items":["sword_01","chest_01","gloves_01","chest_02",{"id":"helmet_01","count":1}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"equips":["sword_01"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"innkeeper","gold":200,"trade":true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"innkeeper","gold":200,"style":"passive_coward","trade":true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"smith","gold":200,"weapon":"sword_01","trade":true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"trader","gold":200,"style":"weak","trade":true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"butcher","gold":200,
+"abilities":["fireball","heal"],"meat":"raw_meat","trade":true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"job":"merchant","gold":200,"trade":true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -987,55 +983,55 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="63">
       <c r="A5" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,157 +1067,157 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="31.5">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>135</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="47.25">
       <c r="A5" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="31.5">
       <c r="A6" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1229,194 +1225,194 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1424,16 +1420,16 @@
         <v>4</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1441,16 +1437,16 @@
         <v>4</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1458,16 +1454,16 @@
         <v>4</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1475,16 +1471,16 @@
         <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1492,16 +1488,16 @@
         <v>4</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1509,16 +1505,16 @@
         <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1526,16 +1522,16 @@
         <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1547,7 +1543,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
@@ -1559,75 +1555,70 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="47.25">
       <c r="A5" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>129</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="31.5">
       <c r="A7" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="31.5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.25">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="47.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B9" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1637,7 +1628,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
@@ -1649,72 +1640,62 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5">
       <c r="A5" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="31.5">
       <c r="A6" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="47.25">
       <c r="A7" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="31.5">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="47.25">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B8" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1725,7 +1706,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
@@ -1737,94 +1718,84 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="31.5">
       <c r="A5" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.5">
       <c r="A6" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="47.25">
       <c r="A7" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="31.5">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="47.25">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="1" r:id="rId1"/>
@@ -543,10 +543,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"meat":"raw_meat","style":"aggressive"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"meat":"raw_meat","style":"skittish"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -607,6 +603,10 @@
   </si>
   <si>
     <t>"job":"merchant","gold":200,"trade":true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"meat":"raw_meat","skin":"plet","style":"aggressive"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -996,7 +996,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>105</v>
@@ -1004,7 +1004,7 @@
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>106</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5" spans="1:2" ht="63">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>112</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1110,30 +1110,30 @@
     </row>
     <row r="3" spans="1:7" ht="31.5">
       <c r="A3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>106</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="5" spans="1:7" ht="47.25">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>110</v>
@@ -1179,22 +1179,22 @@
     </row>
     <row r="6" spans="1:7" ht="31.5">
       <c r="A6" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1568,7 +1568,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>104</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>106</v>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="5" spans="1:2" ht="47.25">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>111</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="31.5">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>104</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="4" spans="1:2" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>117</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="5" spans="1:2" ht="31.5">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>116</v>
@@ -1737,18 +1737,18 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="94.5">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>117</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="5" spans="1:3" ht="31.5">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>120</v>

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="player" state="visible" r:id="rId4"/>
-    <sheet sheetId="4" name="brooklyn" state="visible" r:id="rId5"/>
-    <sheet sheetId="5" name="rogues" state="visible" r:id="rId6"/>
-    <sheet sheetId="2" name="monsters" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="animals" state="visible" r:id="rId8"/>
+    <sheet name="player" sheetId="1" r:id="rId1"/>
+    <sheet name="brooklyn" sheetId="4" r:id="rId2"/>
+    <sheet name="rogues" sheetId="5" r:id="rId3"/>
+    <sheet name="monsters" sheetId="2" r:id="rId4"/>
+    <sheet name="animals" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -41,7 +41,7 @@
     <t>_view</t>
   </si>
   <si>
-    <t xml:space="preserve">"faceR":true,
+    <t>"faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":32, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -52,7 +52,7 @@
     <t>_shape</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"body-man","scale":0.25,"y":32},
+    <t>"body":{"sprite":"body-man","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "head":{"sprite":"head-wick","scale":0.25,"y":3.5},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
@@ -118,39 +118,39 @@
     <t>"job":"trader","gold":200,"style":"weak","trade":true</t>
   </si>
   <si>
-    <t xml:space="preserve">"job":"butcher","gold":200,
+    <t>"job":"butcher","gold":200,
 "abilities":["fireball","heal"],"meat":"raw_meat","trade":true</t>
   </si>
   <si>
     <t>"job":"merchant","gold":200,"trade":true</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"trump","scale":0.25,"y":32},
+    <t>"body":{"sprite":"trump","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"melanie","scale":0.25,"y":32},
+    <t>"body":{"sprite":"melanie","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"musk","scale":0.25,"y":32},
+    <t>"body":{"sprite":"musk","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"xi","scale":0.25,"y":32},
+    <t>"body":{"sprite":"xi","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"macron","scale":0.25,"y":32},
+    <t>"body":{"sprite":"macron","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"storage":{"capacity":-1,
+    <t>"storage":{"capacity":-1,
 "items":["sword_01",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
-    <t xml:space="preserve">"storage":{"capacity":-1,
+    <t>"storage":{"capacity":-1,
 "items":["sword_01","chest_01","gloves_01","chest_02",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
@@ -163,9 +163,6 @@
     <t>"t":"07:40~07:50", "p":"bed~door", "map":"musk-home"</t>
   </si>
   <si>
-    <t>"t":"07:40~07:50", "p":"bed~door", "map":"karen-home"</t>
-  </si>
-  <si>
     <t>"t":"07:40~07:50", "p":"bed~door", "map":"xi-home"</t>
   </si>
   <si>
@@ -358,30 +355,18 @@
     <t>"t":"20:10~20:20", "p":"trump-inn~karen-home", "map":"m/m_04x05"</t>
   </si>
   <si>
-    <t>"t":"20:10~20:20", "p":"trump-inn~xi-home", "map":"m/m_04x05"</t>
-  </si>
-  <si>
     <t>"t":"20:10~20:20", "p":"trump-inn~macron-home", "map":"m/m_04x05"</t>
   </si>
   <si>
     <t>"t":"20:20~20:30", "p":"door~bed", "map":"musk-home"</t>
   </si>
   <si>
-    <t>"t":"20:20~20:30", "p":"door~bed", "map":"karen-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:20~20:30", "p":"door~bed", "map":"xi-home"</t>
-  </si>
-  <si>
     <t>"t":"20:20~20:30", "p":"door~bed", "map":"macron-home"</t>
   </si>
   <si>
     <t>"t":"20:30~07:40", "p":"bed", "map":"musk-home"</t>
   </si>
   <si>
-    <t>"t":"20:30~07:40", "p":"bed", "map":"karen-home"</t>
-  </si>
-  <si>
     <t>"t":"20:30~07:40", "p":"bed", "map":"xi-home"</t>
   </si>
   <si>
@@ -394,7 +379,7 @@
     <t>"job":"rogue","gold":200,"type":"enemy"</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"rogue","scale":0.25,"y":32},
+    <t>"body":{"sprite":"rogue","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
@@ -405,14 +390,14 @@
     <t>attrs</t>
   </si>
   <si>
-    <t xml:space="preserve">"attack": 5,
+    <t>"attack": 5,
 "defense": 0</t>
   </si>
   <si>
     <t>states</t>
   </si>
   <si>
-    <t xml:space="preserve">"life": {"cur":50,"max":50},
+    <t>"life": {"cur":50,"max":50},
 "hunger": {"cur":0,"max":100},
 "thirst": {"cur":0,"max":100}</t>
   </si>
@@ -423,7 +408,7 @@
     <t>monsters:0</t>
   </si>
   <si>
-    <t xml:space="preserve">"faceR":false,
+    <t>"faceR":false,
 "anchor":{"x":-16,"y":16}, 
 "w":64, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -431,7 +416,7 @@
 "z":{"l":0,"r":0,"t":32,"b":0}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"monsters:0","scale":2,"y":32},
+    <t>"body":{"sprite":"monsters:0","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
@@ -453,35 +438,62 @@
     <t>"meat":"raw_meat","style":"skittish"</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"animals:42","scale":2,"y":32},
+    <t>"body":{"sprite":"animals:42","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"animals:82","scale":2,"y":32},
+    <t>"body":{"sprite":"animals:82","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+  </si>
+  <si>
+    <t>"t":"20:10~20:20", "p":"trump-inn~xi-home", "map":"m/m_04x05"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"t":"20:20~20:30", "p":"door~bed", "map":"xi-home"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/karen-home"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"t":"20:20~20:30", "p":"door~bed", "map":"m_04x05/karen-home"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/karen-home"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="微軟正黑體 Light"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -512,12 +524,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -816,16 +828,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="52.875" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -833,7 +846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -841,7 +854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -849,7 +862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="94.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -857,7 +870,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="63" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="63" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,7 +878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -873,7 +886,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -881,759 +894,764 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="63" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="66" style="1" customWidth="1"/>
+    <col min="3" max="3" width="69" style="1" customWidth="1"/>
+    <col min="4" max="4" width="76" style="1" customWidth="1"/>
+    <col min="5" max="5" width="75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="67.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="70.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="94.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="47.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="31.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>111</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.85546875" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="94.5" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="47.25" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.25" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="66" style="1" customWidth="1"/>
-    <col min="3" max="3" width="69" style="1" customWidth="1"/>
-    <col min="4" max="4" width="76" style="1" customWidth="1"/>
-    <col min="5" max="5" width="69" style="1" customWidth="1"/>
-    <col min="6" max="6" width="67.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="70.625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="63" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" ht="94.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="94.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" ht="47.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="31.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="31.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="47.25" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>116</v>
-      </c>
+      <c r="B8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="45.875" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
     <col min="2" max="3" width="63" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" ht="94.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="94.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="31.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="47.25" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1641,6 +1659,7 @@
       <c r="C8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="player" sheetId="1" r:id="rId1"/>
-    <sheet name="brooklyn" sheetId="4" r:id="rId2"/>
-    <sheet name="rogues" sheetId="5" r:id="rId3"/>
-    <sheet name="monsters" sheetId="2" r:id="rId4"/>
-    <sheet name="animals" sheetId="6" r:id="rId5"/>
+    <sheet sheetId="1" name="player" state="visible" r:id="rId4"/>
+    <sheet sheetId="4" name="brooklyn" state="visible" r:id="rId5"/>
+    <sheet sheetId="5" name="rogues" state="visible" r:id="rId6"/>
+    <sheet sheetId="2" name="monsters" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="animals" state="visible" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -41,7 +41,7 @@
     <t>_view</t>
   </si>
   <si>
-    <t>"faceR":true,
+    <t xml:space="preserve">"faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":32, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -52,7 +52,7 @@
     <t>_shape</t>
   </si>
   <si>
-    <t>"body":{"sprite":"body-man","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"body-man","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "head":{"sprite":"head-wick","scale":0.25,"y":3.5},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
@@ -118,39 +118,39 @@
     <t>"job":"trader","gold":200,"style":"weak","trade":true</t>
   </si>
   <si>
-    <t>"job":"butcher","gold":200,
+    <t xml:space="preserve">"job":"butcher","gold":200,
 "abilities":["fireball","heal"],"meat":"raw_meat","trade":true</t>
   </si>
   <si>
     <t>"job":"merchant","gold":200,"trade":true</t>
   </si>
   <si>
-    <t>"body":{"sprite":"trump","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"trump","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"melanie","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"melanie","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"musk","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"musk","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"xi","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"xi","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"macron","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"macron","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"storage":{"capacity":-1,
+    <t xml:space="preserve">"storage":{"capacity":-1,
 "items":["sword_01",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
-    <t>"storage":{"capacity":-1,
+    <t xml:space="preserve">"storage":{"capacity":-1,
 "items":["sword_01","chest_01","gloves_01","chest_02",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
@@ -160,13 +160,16 @@
     <t>"t":"06:10~06:20", "p":"trump-p1~stair-up", "map":"trump-inn-f1"</t>
   </si>
   <si>
-    <t>"t":"07:40~07:50", "p":"bed~door", "map":"musk-home"</t>
-  </si>
-  <si>
-    <t>"t":"07:40~07:50", "p":"bed~door", "map":"xi-home"</t>
-  </si>
-  <si>
-    <t>"t":"07:40~07:50", "p":"bed~door", "map":"macron-home"</t>
+    <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/musk-home"</t>
+  </si>
+  <si>
+    <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/karen-home"</t>
+  </si>
+  <si>
+    <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/xi-home"</t>
+  </si>
+  <si>
+    <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/macron-home"</t>
   </si>
   <si>
     <t>"t":"06:10~06:20", "p":"stair-up~trump-p1", "map":"trump-inn-f1"</t>
@@ -355,22 +358,34 @@
     <t>"t":"20:10~20:20", "p":"trump-inn~karen-home", "map":"m/m_04x05"</t>
   </si>
   <si>
+    <t>"t":"20:10~20:20", "p":"trump-inn~xi-home", "map":"m/m_04x05"</t>
+  </si>
+  <si>
     <t>"t":"20:10~20:20", "p":"trump-inn~macron-home", "map":"m/m_04x05"</t>
   </si>
   <si>
-    <t>"t":"20:20~20:30", "p":"door~bed", "map":"musk-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:20~20:30", "p":"door~bed", "map":"macron-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:30~07:40", "p":"bed", "map":"musk-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:30~07:40", "p":"bed", "map":"xi-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:30~07:40", "p":"bed", "map":"macron-home"</t>
+    <t>"t":"20:20~20:30", "p":"door~bed", "map":"m_04x05/musk-home"</t>
+  </si>
+  <si>
+    <t>"t":"20:20~20:30", "p":"door~bed", "map":"m_04x05/karen-home"</t>
+  </si>
+  <si>
+    <t>"t":"20:20~20:30", "p":"door~bed", "map":"m_04x05/xi-home"</t>
+  </si>
+  <si>
+    <t>"t":"20:20~20:30", "p":"door~bed", "map":"m_04x05/macron-home"</t>
+  </si>
+  <si>
+    <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/musk-home"</t>
+  </si>
+  <si>
+    <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/karen-home"</t>
+  </si>
+  <si>
+    <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/xi-home"</t>
+  </si>
+  <si>
+    <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/macron-home"</t>
   </si>
   <si>
     <t>rogue</t>
@@ -379,7 +394,7 @@
     <t>"job":"rogue","gold":200,"type":"enemy"</t>
   </si>
   <si>
-    <t>"body":{"sprite":"rogue","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"rogue","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
@@ -390,14 +405,14 @@
     <t>attrs</t>
   </si>
   <si>
-    <t>"attack": 5,
+    <t xml:space="preserve">"attack": 5,
 "defense": 0</t>
   </si>
   <si>
     <t>states</t>
   </si>
   <si>
-    <t>"life": {"cur":50,"max":50},
+    <t xml:space="preserve">"life": {"cur":50,"max":50},
 "hunger": {"cur":0,"max":100},
 "thirst": {"cur":0,"max":100}</t>
   </si>
@@ -408,7 +423,7 @@
     <t>monsters:0</t>
   </si>
   <si>
-    <t>"faceR":false,
+    <t xml:space="preserve">"faceR":false,
 "anchor":{"x":-16,"y":16}, 
 "w":64, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -416,7 +431,7 @@
 "z":{"l":0,"r":0,"t":32,"b":0}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"monsters:0","scale":2,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"monsters:0","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
@@ -438,62 +453,35 @@
     <t>"meat":"raw_meat","style":"skittish"</t>
   </si>
   <si>
-    <t>"body":{"sprite":"animals:42","scale":2,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"animals:42","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"animals:82","scale":2,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"animals:82","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
-  </si>
-  <si>
-    <t>"t":"20:10~20:20", "p":"trump-inn~xi-home", "map":"m/m_04x05"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>"t":"20:20~20:30", "p":"door~bed", "map":"xi-home"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/karen-home"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>"t":"20:20~20:30", "p":"door~bed", "map":"m_04x05/karen-home"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/karen-home"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="164" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="微軟正黑體 Light"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -524,12 +512,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -828,17 +816,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="52.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="1"/>
+    <col min="3" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -846,7 +833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -854,7 +841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -862,7 +849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="94.5" customHeight="1">
+    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -870,7 +857,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="63" customHeight="1">
+    <row r="5" ht="63" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -878,7 +865,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -886,7 +873,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -894,23 +881,99 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="63" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="66" style="1" customWidth="1"/>
@@ -919,11 +982,10 @@
     <col min="5" max="5" width="75" style="1" customWidth="1"/>
     <col min="6" max="6" width="67.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="70.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="1"/>
+    <col min="8" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -946,7 +1008,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -969,7 +1031,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.5" customHeight="1">
+    <row r="3" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -992,7 +1054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="94.5" customHeight="1">
+    <row r="4" ht="94.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,7 +1077,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="47.25" customHeight="1">
+    <row r="5" ht="47.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1038,7 +1100,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="31.5" customHeight="1">
+    <row r="6" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1058,7 +1120,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1081,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1095,331 +1157,330 @@
         <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="45.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1427,15 +1488,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75">
+    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="94.5" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1443,215 +1504,136 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="47.25" customHeight="1">
+    <row r="5" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="31.5" customHeight="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="47.25" customHeight="1">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="63" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="94.5" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="31.5" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="31.5" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="47.25" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
     <col min="2" max="3" width="63" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75">
+    <row r="1" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="94.5" customHeight="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="31.5" customHeight="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31.5" customHeight="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="47.25" customHeight="1">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1659,7 +1641,6 @@
       <c r="C8" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -154,10 +154,10 @@
 "items":["sword_01","chest_01","gloves_01","chest_02",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
-    <t>"t":"06:00~06:10", "p":"bed~stair-dn", "map":"trump-inn-f2"</t>
-  </si>
-  <si>
-    <t>"t":"06:10~06:20", "p":"trump-p1~stair-up", "map":"trump-inn-f1"</t>
+    <t>"t":"06:00~06:10", "p":"bed~stair-dn", "map":"m_04x05/trump-inn-f2"</t>
+  </si>
+  <si>
+    <t>"t":"06:10~06:20", "p":"trump-p1~stair-up", "map":"m_04x05/trump-inn-f1"</t>
   </si>
   <si>
     <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/musk-home"</t>
@@ -172,10 +172,10 @@
     <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/macron-home"</t>
   </si>
   <si>
-    <t>"t":"06:10~06:20", "p":"stair-up~trump-p1", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"06:20~06:30", "p":"stair-dn~bed", "map":"trump-inn-f2"</t>
+    <t>"t":"06:10~06:20", "p":"stair-up~trump-p1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"06:20~06:30", "p":"stair-dn~bed", "map":"m_04x05/trump-inn-f2"</t>
   </si>
   <si>
     <t>"t":"07:50~08:00", "p":"musk-home~musk-p1", "map":"m/m_04x05"</t>
@@ -190,10 +190,10 @@
     <t>"t":"07:50~08:00", "p":"macron-home~macron-p1", "map":"m/m_04x05"</t>
   </si>
   <si>
-    <t>"t":"06:20~22:30", "p":"trump-p1", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"06:30~14:30", "p":"bed", "map":"trump-inn-f2"</t>
+    <t>"t":"06:20~22:30", "p":"trump-p1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"06:30~14:30", "p":"bed", "map":"m_04x05/trump-inn-f2"</t>
   </si>
   <si>
     <t>"t":"08:00~11:50", "p":"musk-p1", "map":"m/m_04x05"</t>
@@ -208,10 +208,10 @@
     <t>"t":"08:00~11:50", "p":"macron-p1", "map":"m/m_04x05"</t>
   </si>
   <si>
-    <t>"t":"22:30~22:40", "p":"trump-p1~stair-up", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"14:30~14:40", "p":"bed~stair-dn", "map":"trump-inn-f2"</t>
+    <t>"t":"22:30~22:40", "p":"trump-p1~stair-up", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"14:30~14:40", "p":"bed~stair-dn", "map":"m_04x05/trump-inn-f2"</t>
   </si>
   <si>
     <t>"t":"11:50~12:00", "p":"musk-p1~trump-inn", "map":"m/m_04x05"</t>
@@ -226,58 +226,58 @@
     <t>"t":"11:50~12:00", "p":"macron-p1~trump-inn", "map":"m/m_04x05"</t>
   </si>
   <si>
-    <t>"t":"22:40~22:50", "p":"stair-dn~bed", "map":"trump-inn-f2"</t>
-  </si>
-  <si>
-    <t>"t":"14:40~14:50", "p":"stair-up~melanie-p1", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:00~12:10", "p":"door~sit-1", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:00~12:10", "p":"door~sit-3", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:00~12:10", "p":"door~sit-5", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:00~12:10", "p":"door~sit-7", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"22:50~06:00", "p":"bed", "map":"trump-inn-f2"</t>
-  </si>
-  <si>
-    <t>"t":"14:50~22:30", "p":"melanie-p1", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:10~13:00", "p":"sit-1", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:10~13:00", "p":"sit-3", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:10~13:00", "p":"sit-5", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:10~13:00", "p":"sit-7", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"22:30~22:40", "p":"melanie-p1~trump-p1", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"13:00~13:10", "p":"sit-1~door", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"13:00~13:10", "p":"sit-3~door", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"13:00~13:10", "p":"sit-5~door", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"13:00~13:10", "p":"sit-7~door", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"22:40~06:10", "p":"trump-p1", "map":"trump-inn-f1"</t>
+    <t>"t":"22:40~22:50", "p":"stair-dn~bed", "map":"m_04x05/trump-inn-f2"</t>
+  </si>
+  <si>
+    <t>"t":"14:40~14:50", "p":"stair-up~melanie-p1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"12:00~12:10", "p":"door~sit-1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"12:00~12:10", "p":"door~sit-3", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"12:00~12:10", "p":"door~sit-5", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"12:00~12:10", "p":"door~sit-7", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"22:50~06:00", "p":"bed", "map":"m_04x05/trump-inn-f2"</t>
+  </si>
+  <si>
+    <t>"t":"14:50~22:30", "p":"melanie-p1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"12:10~13:00", "p":"sit-1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"12:10~13:00", "p":"sit-3", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"12:10~13:00", "p":"sit-5", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"12:10~13:00", "p":"sit-7", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"22:30~22:40", "p":"melanie-p1~trump-p1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"13:00~13:10", "p":"sit-1~door", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"13:00~13:10", "p":"sit-3~door", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"13:00~13:10", "p":"sit-5~door", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"13:00~13:10", "p":"sit-7~door", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"22:40~06:10", "p":"trump-p1", "map":"m_04x05/trump-inn-f1"</t>
   </si>
   <si>
     <t>"t":"13:10~13:20", "p":"trump-inn~musk-p1", "map":"m/m_04x05"</t>
@@ -316,40 +316,40 @@
     <t>"t":"17:00~17:10", "p":"macron-p1~trump-inn", "map":"m/m_04x05"</t>
   </si>
   <si>
-    <t>"t":"17:10~17:20", "p":"door~sit-1", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:10~17:20", "p":"door~sit-3", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:10~17:20", "p":"door~sit-5", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:10~17:20", "p":"door~sit-7", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:20~20:00", "p":"sit-1", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:20~20:00", "p":"sit-3", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:20~20:00", "p":"sit-5", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:20~20:00", "p":"sit-7", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"20:00~20:10", "p":"sit-1~door", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"20:00~20:10", "p":"sit-3~door", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"20:00~20:10", "p":"sit-5~door", "map":"trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"20:00~20:10", "p":"sit-7~door", "map":"trump-inn-f1"</t>
+    <t>"t":"17:10~17:20", "p":"door~sit-1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"17:10~17:20", "p":"door~sit-3", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"17:10~17:20", "p":"door~sit-5", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"17:10~17:20", "p":"door~sit-7", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"17:20~20:00", "p":"sit-1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"17:20~20:00", "p":"sit-3", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"17:20~20:00", "p":"sit-5", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"17:20~20:00", "p":"sit-7", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"20:00~20:10", "p":"sit-1~door", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"20:00~20:10", "p":"sit-3~door", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"20:00~20:10", "p":"sit-5~door", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"20:00~20:10", "p":"sit-7~door", "map":"m_04x05/trump-inn-f1"</t>
   </si>
   <si>
     <t>"t":"20:10~20:20", "p":"trump-inn~musk-home", "map":"m/m_04x05"</t>

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="player" state="visible" r:id="rId4"/>
-    <sheet sheetId="4" name="brooklyn" state="visible" r:id="rId5"/>
-    <sheet sheetId="5" name="rogues" state="visible" r:id="rId6"/>
-    <sheet sheetId="2" name="monsters" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="animals" state="visible" r:id="rId8"/>
+    <sheet name="player" sheetId="1" r:id="rId1"/>
+    <sheet name="brooklyn" sheetId="4" r:id="rId2"/>
+    <sheet name="rogues" sheetId="5" r:id="rId3"/>
+    <sheet name="monsters" sheetId="2" r:id="rId4"/>
+    <sheet name="animals" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="139">
   <si>
     <t>id</t>
   </si>
@@ -41,7 +41,7 @@
     <t>_view</t>
   </si>
   <si>
-    <t xml:space="preserve">"faceR":true,
+    <t>"faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":32, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -52,7 +52,7 @@
     <t>_shape</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"body-man","scale":0.25,"y":32},
+    <t>"body":{"sprite":"body-man","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "head":{"sprite":"head-wick","scale":0.25,"y":3.5},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
@@ -118,39 +118,39 @@
     <t>"job":"trader","gold":200,"style":"weak","trade":true</t>
   </si>
   <si>
-    <t xml:space="preserve">"job":"butcher","gold":200,
+    <t>"job":"butcher","gold":200,
 "abilities":["fireball","heal"],"meat":"raw_meat","trade":true</t>
   </si>
   <si>
     <t>"job":"merchant","gold":200,"trade":true</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"trump","scale":0.25,"y":32},
+    <t>"body":{"sprite":"trump","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"melanie","scale":0.25,"y":32},
+    <t>"body":{"sprite":"melanie","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"musk","scale":0.25,"y":32},
+    <t>"body":{"sprite":"musk","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"xi","scale":0.25,"y":32},
+    <t>"body":{"sprite":"xi","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"macron","scale":0.25,"y":32},
+    <t>"body":{"sprite":"macron","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"storage":{"capacity":-1,
+    <t>"storage":{"capacity":-1,
 "items":["sword_01",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
-    <t xml:space="preserve">"storage":{"capacity":-1,
+    <t>"storage":{"capacity":-1,
 "items":["sword_01","chest_01","gloves_01","chest_02",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
@@ -388,31 +388,23 @@
     <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/macron-home"</t>
   </si>
   <si>
-    <t>rogue</t>
-  </si>
-  <si>
     <t>"job":"rogue","gold":200,"type":"enemy"</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"rogue","scale":0.25,"y":32},
-"hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
-  </si>
-  <si>
     <t>"equips":["sword_01"]</t>
   </si>
   <si>
     <t>attrs</t>
   </si>
   <si>
-    <t xml:space="preserve">"attack": 5,
+    <t>"attack": 5,
 "defense": 0</t>
   </si>
   <si>
     <t>states</t>
   </si>
   <si>
-    <t xml:space="preserve">"life": {"cur":50,"max":50},
+    <t>"life": {"cur":50,"max":50},
 "hunger": {"cur":0,"max":100},
 "thirst": {"cur":0,"max":100}</t>
   </si>
@@ -423,7 +415,7 @@
     <t>monsters:0</t>
   </si>
   <si>
-    <t xml:space="preserve">"faceR":false,
+    <t>"faceR":false,
 "anchor":{"x":-16,"y":16}, 
 "w":64, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -431,7 +423,7 @@
 "z":{"l":0,"r":0,"t":32,"b":0}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"monsters:0","scale":2,"y":32},
+    <t>"body":{"sprite":"monsters:0","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
@@ -453,35 +445,60 @@
     <t>"meat":"raw_meat","style":"skittish"</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"animals:42","scale":2,"y":32},
+    <t>"body":{"sprite":"animals:42","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"animals:82","scale":2,"y":32},
+    <t>"body":{"sprite":"animals:82","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+  </si>
+  <si>
+    <t>"body":{"sprite":"rogue","scale":0.25,"y":32},
+"hand":{"sprite":"hand-man","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rogue-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rogue-2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"equips":["bow_01"]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="微軟正黑體 Light"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -512,12 +529,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -816,16 +833,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="52.85546875" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -833,7 +851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -841,7 +859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -849,7 +867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="94.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -857,7 +875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="63" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="63" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,7 +883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -873,7 +891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -881,99 +899,23 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="63" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="66" style="1" customWidth="1"/>
@@ -982,10 +924,11 @@
     <col min="5" max="5" width="75" style="1" customWidth="1"/>
     <col min="6" max="6" width="67.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="70.5703125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1008,7 +951,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1031,7 +974,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1054,7 +997,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" ht="94.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="94.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,7 +1020,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="47.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="47.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1100,7 +1043,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="31.5" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1120,7 +1063,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1143,7 +1086,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1166,7 +1109,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1189,7 +1132,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,7 +1155,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1235,7 +1178,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1258,7 +1201,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1281,7 +1224,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -1301,7 +1244,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1321,7 +1264,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -1338,7 +1281,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1355,7 +1298,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
@@ -1372,7 +1315,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1389,7 +1332,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1406,7 +1349,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
@@ -1423,7 +1366,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
         <v>14</v>
       </c>
@@ -1440,7 +1383,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
         <v>14</v>
       </c>
@@ -1458,182 +1401,288 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="94.5" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="47.25" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="31.5" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="47.25" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="63" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="94.5" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="47.25" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="45.85546875" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
     <col min="2" max="3" width="63" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" ht="94.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="94.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="31.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.5" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="47.25" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="7" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1641,6 +1690,7 @@
       <c r="C8" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>